--- a/reports/pdf_rolling5_20261007.xlsx
+++ b/reports/pdf_rolling5_20261007.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,293억   ·   현금 5억(0.1%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 8종목  /  매도 19종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 5,416억   ·   현금 3억(0.0%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 8종목  /  매도 19종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>125</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>1923188368</v>
+        <v>1921215828</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-136</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-4515032038</v>
+        <v>-4510401145</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>104</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8811663977</v>
+        <v>8802626196</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-73</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2081869690</v>
+        <v>-2079734397</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>61</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1159763023</v>
+        <v>1158573500</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-35</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1254094316</v>
+        <v>-1252808040</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3166801429</v>
+        <v>3163553364</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-31</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-484506969</v>
+        <v>-484010029</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>24</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>2014740909</v>
+        <v>2012674468</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-28</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1441440650</v>
+        <v>-1439962221</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>20</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>837525378</v>
+        <v>836666361</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-28</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-312312141</v>
+        <v>-311991815</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>549120248</v>
+        <v>548557037</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-985530445</v>
+        <v>-984519625</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>867262891</v>
+        <v>866373374</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-13</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-85809789</v>
+        <v>-85721777</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1008150455</v>
+        <v>-1038187048</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.81%</t>
+          <t>0.80%→0.54%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1039252969</v>
+        <v>-1007116434</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.54%</t>
+          <t>1.01%→0.81%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
         <v>-9</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-736222832</v>
+        <v>-735467717</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>-8</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-317460143</v>
+        <v>-317134537</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>-7</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-204067592</v>
+        <v>-203858288</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-138645063</v>
+        <v>-138502860</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
@@ -1188,23 +1188,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-558090252</v>
+        <v>-137626259</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.43%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-137767562</v>
+        <v>-557517840</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>0.52%→0.43%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         <v>-5</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-1267500572</v>
+        <v>-1266200546</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
         <v>-4</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-768300347</v>
+        <v>-767512331</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>-3</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-895050404</v>
+        <v>-894132386</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,381억   ·   현금 55억(1.6%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 8종목  /  매도 7종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,499억   ·   현금 28억(0.8%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1419,7 +1419,7 @@
         <v>122</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>1837613362</v>
+        <v>1848153951</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>-258</v>
       </c>
       <c r="I29" s="15" t="n">
-        <v>-2365393744</v>
+        <v>-2378961692</v>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>119</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>1820432807</v>
+        <v>1830874848</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1484,7 +1484,7 @@
         <v>-233</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-971216527</v>
+        <v>-976787446</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1507,7 +1507,7 @@
         <v>95</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>2181172167</v>
+        <v>2193683417</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
         <v>-122</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1022810493</v>
+        <v>-1028677356</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>37</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>1015927811</v>
+        <v>1021755194</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
         <v>-70</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-1019588812</v>
+        <v>-1025437195</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>17</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>348082756</v>
+        <v>350079367</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>-20</v>
       </c>
       <c r="I33" s="15" t="n">
-        <v>-1013574310</v>
+        <v>-1019388194</v>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         <v>13</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>324992299</v>
+        <v>326856462</v>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
         <v>-19</v>
       </c>
       <c r="I34" s="15" t="n">
-        <v>-313015596</v>
+        <v>-314811060</v>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>10</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>953952292</v>
+        <v>959424182</v>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
         <v>-16</v>
       </c>
       <c r="I35" s="15" t="n">
-        <v>-1025917114</v>
+        <v>-1031801796</v>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>323423299</v>
+        <v>325278462</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
     <row r="38" ht="19" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,842억   ·   현금 85억(2.9%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,947억   ·   현금 43억(1.4%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B38" s="4" t="n"/>
@@ -1772,7 +1772,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,093억   ·   현금 18억(0.8%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 4종목  /  매도 5종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,198억   ·   현금 9억(0.4%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 4종목  /  매도 5종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>
@@ -1868,7 +1868,7 @@
         <v>456</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>7226645603</v>
+        <v>7386790401</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>-205</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2912098041</v>
+        <v>-2976631073</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
@@ -1912,7 +1912,7 @@
         <v>279</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>2789917537</v>
+        <v>2851743009</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>-60</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2098854930</v>
+        <v>-2145366233</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>221</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>2333595284</v>
+        <v>2385308509</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>-45</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-852862878</v>
+        <v>-871762594</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>31</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>2041239305</v>
+        <v>2086473826</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2021,7 +2021,7 @@
         <v>-27</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-5097683259</v>
+        <v>-5210649565</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
         <v>-12</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-669727497</v>
+        <v>-684568874</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 316억   ·   현금 4억(1.1%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 7종목  /  매도 8종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 325억   ·   현금 2억(0.6%)      오늘 2026-10-07  vs  5일전 2026-09-29      매수 7종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B50" s="4" t="n"/>
@@ -2161,11 +2161,11 @@
         <v>111</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>81593856</v>
+        <v>81669360</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>7.07%→7.35%</t>
+          <t>6.90%→7.17%</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -2182,11 +2182,11 @@
         <v>-152</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-115143006</v>
+        <v>-124858880</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>1.89%→1.53%</t>
+          <t>2.00%→1.61%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -2205,11 +2205,11 @@
         <v>58</v>
       </c>
       <c r="C54" s="11" t="n">
-        <v>87951174</v>
+        <v>98008400</v>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>2.13%→2.41%</t>
+          <t>2.31%→2.62%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -2226,11 +2226,11 @@
         <v>-68</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-191895944</v>
+        <v>-198600800</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>8.17%→7.58%</t>
+          <t>8.24%→7.65%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -2249,11 +2249,11 @@
         <v>35</v>
       </c>
       <c r="C55" s="11" t="n">
-        <v>64259981</v>
+        <v>64379000</v>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>4.85%→5.06%</t>
+          <t>4.74%→4.95%</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -2270,11 +2270,11 @@
         <v>-33</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-47236186</v>
+        <v>-45665400</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>3.84%→3.69%</t>
+          <t>3.61%→3.48%</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -2293,7 +2293,7 @@
         <v>34</v>
       </c>
       <c r="C56" s="11" t="n">
-        <v>94676372</v>
+        <v>96757200</v>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
@@ -2314,11 +2314,11 @@
         <v>-14</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-39222388</v>
+        <v>-39603200</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.21%→2.09%</t>
+          <t>2.18%→2.06%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -2337,11 +2337,11 @@
         <v>31</v>
       </c>
       <c r="C57" s="11" t="n">
-        <v>78206777</v>
+        <v>77469000</v>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>1.02%→1.27%</t>
+          <t>0.98%→1.22%</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -2358,11 +2358,11 @@
         <v>-9</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-108568768</v>
+        <v>-107956800</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.98%→2.65%</t>
+          <t>2.89%→2.56%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
@@ -2374,23 +2374,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>57391983</v>
+        <v>82144000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.17%→2.35%</t>
+          <t>3.80%→4.06%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2402,11 +2402,11 @@
         <v>-7</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-31463591</v>
+        <v>-33510400</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>2.85%→2.76%</t>
+          <t>2.96%→2.86%</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -2418,23 +2418,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>80375976</v>
+        <v>61676000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>3.81%→4.07%</t>
+          <t>2.27%→2.46%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2446,11 +2446,11 @@
         <v>-6</v>
       </c>
       <c r="I59" s="15" t="n">
-        <v>-43615187</v>
+        <v>-48960000</v>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>2.21%→2.08%</t>
+          <t>2.42%→2.28%</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -2474,11 +2474,11 @@
         <v>-5</v>
       </c>
       <c r="I60" s="15" t="n">
-        <v>-32231991</v>
+        <v>-31960000</v>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>1.33%→1.23%</t>
+          <t>1.28%→1.19%</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="64" ht="19" customHeight="1">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,175억      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,223억      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B64" s="4" t="n"/>

--- a/reports/pdf_rolling5_20261007.xlsx
+++ b/reports/pdf_rolling5_20261007.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-29 ~ 2026-10-07  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
+          <t>최근 5거래일 변화  ·  2026-09-29 ~ 2026-10-07  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
         </is>
       </c>
     </row>
@@ -1020,23 +1020,23 @@
       <c r="E14" s="17" t="n"/>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>에스티팜</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="H14" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1038187048</v>
+        <v>-1007116434</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>0.80%→0.54%</t>
+          <t>1.01%→0.81%</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>42→31</t>
+          <t>59→48</t>
         </is>
       </c>
     </row>
@@ -1048,23 +1048,23 @@
       <c r="E15" s="17" t="n"/>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>에스티팜</t>
         </is>
       </c>
       <c r="H15" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-1007116434</v>
+        <v>-1038187048</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.81%</t>
+          <t>0.80%→0.54%</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>59→48</t>
+          <t>42→31</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-138502860</v>
+        <v>-557517840</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.41%</t>
+          <t>0.52%→0.43%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>102→96</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-557517840</v>
+        <v>-138502860</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.43%</t>
+          <t>0.48%→0.41%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>102→96</t>
         </is>
       </c>
     </row>
@@ -2505,50 +2505,42 @@
       <c r="K62" s="20" t="n"/>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,223억      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
-        </is>
-      </c>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="18" t="inlineStr">
-        <is>
-          <t>변화 없음 (구성종목 동일)</t>
-        </is>
-      </c>
+      <c r="A64" s="19" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
+        </is>
+      </c>
+      <c r="B64" s="20" t="n"/>
+      <c r="C64" s="20" t="n"/>
+      <c r="D64" s="20" t="n"/>
+      <c r="E64" s="20" t="n"/>
+      <c r="F64" s="20" t="n"/>
+      <c r="G64" s="20" t="n"/>
+      <c r="H64" s="20" t="n"/>
+      <c r="I64" s="20" t="n"/>
+      <c r="J64" s="20" t="n"/>
+      <c r="K64" s="20" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="18">
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A26:K26"/>
     <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A41:K41"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A41:K41"/>
     <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A50:K50"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A42:E42"/>
-    <mergeCell ref="A2:K2"/>
     <mergeCell ref="G4:K4"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="G51:K51"/>
-    <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A38:K38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261007.xlsx
+++ b/reports/pdf_rolling5_20261007.xlsx
@@ -1188,23 +1188,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-137626259</v>
+        <v>-138502860</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>0.48%→0.41%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>102→96</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-138502860</v>
+        <v>-137626259</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.41%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>102→96</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261007.xlsx
+++ b/reports/pdf_rolling5_20261007.xlsx
@@ -541,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-09-29 ~ 2026-10-07  (최근 5거래일)  ·  캡처 5/7  ·  대기: RISE, TIGER</t>
+          <t>최근 5거래일 변화  ·  2026-09-29 ~ 2026-10-07  (최근 5거래일)  ·  캡처 6/7  ·  대기: RISE</t>
         </is>
       </c>
     </row>
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1439962221</v>
+        <v>-311991815</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.10%</t>
+          <t>1.60%→1.39%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>39→11</t>
+          <t>701→673</t>
         </is>
       </c>
     </row>
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-311991815</v>
+        <v>-1439962221</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>1.60%→1.39%</t>
+          <t>0.36%→0.10%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>701→673</t>
+          <t>39→11</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-557517840</v>
+        <v>-137626259</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.43%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1188,23 +1188,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-138502860</v>
+        <v>-557517840</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.41%</t>
+          <t>0.52%→0.43%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>102→96</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-137626259</v>
+        <v>-138502860</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>0.48%→0.41%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>102→96</t>
         </is>
       </c>
     </row>
@@ -2374,23 +2374,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>82144000</v>
+        <v>61676000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>3.80%→4.06%</t>
+          <t>2.27%→2.46%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2418,23 +2418,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>61676000</v>
+        <v>82144000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>2.27%→2.46%</t>
+          <t>3.80%→4.06%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -2505,42 +2505,50 @@
       <c r="K62" s="20" t="n"/>
     </row>
     <row r="64" ht="19" customHeight="1">
-      <c r="A64" s="19" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B64" s="20" t="n"/>
-      <c r="C64" s="20" t="n"/>
-      <c r="D64" s="20" t="n"/>
-      <c r="E64" s="20" t="n"/>
-      <c r="F64" s="20" t="n"/>
-      <c r="G64" s="20" t="n"/>
-      <c r="H64" s="20" t="n"/>
-      <c r="I64" s="20" t="n"/>
-      <c r="J64" s="20" t="n"/>
-      <c r="K64" s="20" t="n"/>
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,223억      오늘 2026-10-07  vs  5일전 2026-09-29      매수 0종목  /  매도 0종목</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="n"/>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>변화 없음 (구성종목 동일)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="19">
+    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A65:K65"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A27:E27"/>
     <mergeCell ref="A50:K50"/>
-    <mergeCell ref="G51:K51"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A26:K26"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A42:E42"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G51:K51"/>
     <mergeCell ref="A62:K62"/>
-    <mergeCell ref="A64:K64"/>
-    <mergeCell ref="A42:E42"/>
     <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A41:K41"/>
-    <mergeCell ref="G42:K42"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="G4:K4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261007.xlsx
+++ b/reports/pdf_rolling5_20261007.xlsx
@@ -860,23 +860,23 @@
       </c>
       <c r="G10" s="14" t="inlineStr">
         <is>
-          <t>서부T&amp;D</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="H10" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-311991815</v>
+        <v>-1439962221</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>1.60%→1.39%</t>
+          <t>0.36%→0.10%</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>701→673</t>
+          <t>39→11</t>
         </is>
       </c>
     </row>
@@ -904,23 +904,23 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>하나마이크론</t>
+          <t>서부T&amp;D</t>
         </is>
       </c>
       <c r="H11" s="15" t="n">
         <v>-28</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-1439962221</v>
+        <v>-311991815</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.10%</t>
+          <t>1.60%→1.39%</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>39→11</t>
+          <t>701→673</t>
         </is>
       </c>
     </row>
@@ -1160,23 +1160,23 @@
       <c r="E19" s="17" t="n"/>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>한텍</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-137626259</v>
+        <v>-138502860</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.46%→0.38%</t>
+          <t>0.48%→0.41%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>96→90</t>
+          <t>102→96</t>
         </is>
       </c>
     </row>
@@ -1188,23 +1188,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에코프로</t>
+          <t>한텍</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-557517840</v>
+        <v>-137626259</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.43%</t>
+          <t>0.46%→0.38%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>31→25</t>
+          <t>96→90</t>
         </is>
       </c>
     </row>
@@ -1216,23 +1216,23 @@
       <c r="E21" s="17" t="n"/>
       <c r="G21" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>에코프로</t>
         </is>
       </c>
       <c r="H21" s="15" t="n">
         <v>-6</v>
       </c>
       <c r="I21" s="15" t="n">
-        <v>-138502860</v>
+        <v>-557517840</v>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>0.48%→0.41%</t>
+          <t>0.52%→0.43%</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>102→96</t>
+          <t>31→25</t>
         </is>
       </c>
     </row>
@@ -2374,23 +2374,23 @@
     <row r="58">
       <c r="A58" s="10" t="inlineStr">
         <is>
-          <t>한중엔시에스</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B58" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C58" s="11" t="n">
-        <v>61676000</v>
+        <v>82144000</v>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>2.27%→2.46%</t>
+          <t>3.80%→4.06%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>238→258</t>
+          <t>299→319</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -2418,23 +2418,23 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>한중엔시에스</t>
         </is>
       </c>
       <c r="B59" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C59" s="11" t="n">
-        <v>82144000</v>
+        <v>61676000</v>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>3.80%→4.06%</t>
+          <t>2.27%→2.46%</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>299→319</t>
+          <t>238→258</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
